--- a/checklist_app/static/checklist_app/sample_import_questions.xlsx
+++ b/checklist_app/static/checklist_app/sample_import_questions.xlsx
@@ -39,12 +39,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00009EF7"/>
-        <bgColor rgb="00009EF7"/>
+        <fgColor rgb="0000B0F0"/>
+        <bgColor rgb="0000B0F0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -52,22 +52,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -435,25 +426,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>متن سوال</t>
@@ -461,7 +452,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>محدوده</t>
+          <t>محدوده‌ها</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -471,17 +462,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>نوع ماشین</t>
+          <t>انواع ماشین</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>بخش مکانی</t>
+          <t>بخش‌های مکانی</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>دسته‌بندی خودرو</t>
+          <t>دسته‌بندی‌های خودرو</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -520,286 +511,353 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>آیا سیستم روشنایی ماشین سالم است؟</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>ماشین</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>گزینه‌ای</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>دامپتراک</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>سالم است,نیاز به تعمیر دارد,خراب است</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>نیاز به تعمیر دارد,خراب است</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>سالم است, نیاز به تعمیر دارد, خراب است</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>نیاز به تعمیر دارد, خراب است</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>نقص فنی</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>نقص در سیستم روشنایی ماشین</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>تعمیر یا تعویض سیستم روشنایی</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>آیا کپسول آتش‌نشانی در محل نصب شده است؟</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>آیا کمپرس آب‌پاشی در محل نصب شده است؟</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>مکان</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>گزینه‌ای</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>انبار مواد شیمیایی</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>نصب شده است,نصب نشده است,نیاز به شارژ دارد</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>نصب نشده است,نیاز به شارژ دارد</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ابزار مواد شیمیایی</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>نصب شده است, نصب نشده است</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>نصب نشده است</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>ایمنی</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>عدم وجود یا نقص در کپسول آتش‌نشانی</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>عدم وجود یا نقص در کمپرس آب‌پاشی</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>فوری</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>نصب یا شارژ کپسول آتش‌نشانی</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>نصب یا تعمیر کمپرس آب‌پاشی</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>وضعیت ترمز ماشین چگونه است؟</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>وضعیت قرار ماشین پیمانکار چگونه است؟</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>ماشین‌آلات پیمانکار</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>گزینه‌ای</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
         <is>
           <t>ماشین‌آلات معدنی</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>سالم است,نیاز به تنظیم دارد,خراب است</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>نیاز به تنظیم دارد,خراب است</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>سالم است, نیاز به تنظیم دارد, خراب است</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>نیاز به تنظیم دارد, خراب است</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>نقص فنی</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>نقص در سیستم ترمز</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>نقص در سیستم پیمانکار</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>فوری</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>تعمیر یا تنظیم سیستم ترمز</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>تعمیر یا تنظیم سیستم پیمانکار</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>میزان آلودگی صوتی را ثبت کنید</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>مکان</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>متنی</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
         <is>
           <t>سالن تولید</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ایمنی</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>آلودگی صوتی بالاتر از حد مجاز</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>نصب عایق صوتی و تجهیزات کاهش صدا</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>آیا کمربند ایمنی راننده سالم است؟</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>ماشین‌آلات پیمانکار</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>گزینه‌ای</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
         <is>
           <t>خودروهای سبک</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>سالم است,نیاز به تعمیر دارد,خراب است</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>نیاز به تعمیر دارد,خراب است</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>سالم است, نیاز به تعمیر دارد, خراب است</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>نیاز به تعمیر دارد, خراب است</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>ایمنی</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>نقص در کمربند ایمنی</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>فوری</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>تعمیر یا تعویض کمربند ایمنی</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>آیا دستگاه سالم است؟</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ماشین, ماشین‌آلات پیمانکار</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>گزینه‌ای</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>دامپتراک, لودر</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ماشین‌آلات معدنی, خودروهای سبک</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>سالم است, نیاز به تعمیر دارد, خراب است</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>نیاز به تعمیر دارد, خراب است</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>نقص فنی</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>نقص در دستگاه</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>تعمیر یا تعویض قطعه</t>
         </is>
       </c>
     </row>
